--- a/contractor_forms/003_moving_items_information_form--contractor_forms.xlsx
+++ b/contractor_forms/003_moving_items_information_form--contractor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -946,12 +946,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>item_serial_number</t>
+          <t>item_serial_number_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Item Serial Number</t>
+          <t>Item Serial Number 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>item_weight</t>
+          <t>item_weight_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Item Weight</t>
+          <t>Item Weight 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>item_size</t>
+          <t>item_size_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Item Size</t>
+          <t>Item Size 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>item_description</t>
+          <t>item_description_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Item Description</t>
+          <t>Item Description 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>item_value</t>
+          <t>item_value_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Item Value</t>
+          <t>Item Value 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>item_warranty_start</t>
+          <t>item_warranty_start_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>item_status</t>
+          <t>item_status_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Item Status</t>
+          <t>Item Status 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1320,7 +1320,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>item_status_choices</t>
+          <t>item_status_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1337,7 +1337,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>item_status_choices</t>
+          <t>item_status_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
